--- a/data.mn/public/datasets/mongolbank-new-issued-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-new-issued-loans.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2325,4 +2326,1924 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B190"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>шинэ_зээлийн_олголт_тэрбум_төгрөг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2000-03-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24.535</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2000-06-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>49.279</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2000-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>66.54900000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>36.513</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>45.531</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60.167</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2001-09-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>58.115</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2001-12-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>95.414</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2002-03-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>88.672</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2002-06-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>124.032</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2002-09-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>105.898</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2002-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>151.297</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>150.965</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2003-06-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>183.837</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2003-09-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>162.708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2003-12-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>217.222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>235.101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>260.625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>226.101</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>277.768</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>263.084</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>329.235</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>353.527</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>453.243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>399.477</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>504.929</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>457.029</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>573.085</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>648.2380000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>939.053</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>885.9349999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1041.46</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1045.336</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1040.653</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>920.592</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>604.582</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>451.628</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>593.241</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>802.329</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>816.975</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>681.736</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>936.428</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>936.701</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1211.731</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1446.932</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2222.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1751.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1904.972</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1362.826</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2061.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1857.404</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1885.658</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1781.224</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3214.133</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3259.986</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3140.578</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2364.541</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3347.312</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2866.949</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2966.915</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2168.857</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2521.795</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2560.352</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2239.924</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2290.635</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>820.629</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>998.494</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1420.657</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>745.121</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1133.167</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>790.869</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>731.26</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>986.782</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1376.133</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>790.457</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1123.044</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>964.123</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1014.352</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1314.557</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1389.098</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>951.961</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1444.63</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1171.065</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1256.521</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1144.367</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1648.306</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1197.915</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1265.883</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1414.02</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1537.824</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2135.845</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2166.054</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1556.273</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1954.389</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1801.277</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2086.538</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2146.857</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2875.31</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1497.209</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1075.438</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1674.385</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1918.774</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2003.933</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2043.129</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1767.648</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1848.296</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1493.058</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2018.159</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1649.835</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2050.283</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1497.892</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1342.958</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1300.079</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1516.966</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1782.205</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1981.987</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1904.488</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1593.643</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1819.118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1801.922</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1274.003</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1965.604</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1441.947</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1390.759</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2408.559</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1886.975</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2937.606</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3443.526</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2452.528</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2448.026</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2337.952</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2134.164</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2423.431</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3009.885</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2360.283</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1845.671</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3170.062</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2968.046</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3253.916</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2749.95</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2117.165</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2511.578</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2524.705</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2414.561</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2690.376</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2762.912</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2615.509</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2801.822</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>3099.286</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3026.005</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3893.107</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4168.737</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3015.333</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3857.107</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3500.927</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3722.729</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3647.241</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4416.639</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3896.335</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3315.461</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>4450.809</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>4807.714</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>5574.867</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>5880.879</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4652.297</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>4780.967</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4537.179</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>4886.198</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4372.266</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>5945.713</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>4751.468</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>5457.558</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>4492.6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>5771.624</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>5801.517</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6554.64</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5233.345</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5245.403</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>5615.405</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>6102.414</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>4993.547</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>6670.921</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>5497.105</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4260.444</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5969.527</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6829.825</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7268.852</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>8102.759</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>5840.364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/mongolbank-new-issued-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-new-issued-loans.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2321,26 @@
       </c>
       <c r="B190" t="n">
         <v>5840.364</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>6808.517</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>7116.877</v>
       </c>
     </row>
   </sheetData>
@@ -2334,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4243,6 +4263,26 @@
         <v>5840.364</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>6808.517</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>7116.877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
